--- a/참고사항/SysClk_Timing_Calc.xlsx
+++ b/참고사항/SysClk_Timing_Calc.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="SysClk_타이밍계산" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -69,127 +69,128 @@
     <t>비고</t>
   </si>
   <si>
+    <t>SCL High 최소 유지시간</t>
+  </si>
+  <si>
+    <t>ClkDivider: SCL High 상태 유지 클럭 수</t>
+  </si>
+  <si>
+    <t>TLOW</t>
+  </si>
+  <si>
+    <t>SCL Low 최소 유지시간</t>
+  </si>
+  <si>
+    <t>ClkDivider: SCL Low 상태 유지 클럭 수</t>
+  </si>
+  <si>
+    <t>THD:STA</t>
+  </si>
+  <si>
+    <t>START 생성 후 첫 SCL Low까지 대기</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: START 직후 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>TSU:STA</t>
+  </si>
+  <si>
+    <t>(Repeated)START 전 SDA High 유지</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: Repeated START 전 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>TSU:DAT</t>
+  </si>
+  <si>
+    <t>SDA 변경 후 SCL 상승까지 여유</t>
+  </si>
+  <si>
+    <t>BitTxRx: SDA 바꾼 후 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>보통 TLOW 안에서 자동 확보됨</t>
+  </si>
+  <si>
+    <t>THD:DAT</t>
+  </si>
+  <si>
+    <t>SCL 하강 후 SDA 변경까지 여유</t>
+  </si>
+  <si>
+    <t>BitTxRx: 사실상 제약 없음</t>
+  </si>
+  <si>
+    <t>0이라 대기 불필요</t>
+  </si>
+  <si>
+    <t>TSU:STO</t>
+  </si>
+  <si>
+    <t>STOP 생성 전 SCL High 유지</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: STOP 만들기 전 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>TBUF</t>
+  </si>
+  <si>
+    <t>STOP~다음 START 최소 간격</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: 트랜잭션 사이 최소 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>참고용 (FSM 카운터에 직접 안 들어감)</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>SDA/SCL rise time (물리적 특성)</t>
+  </si>
+  <si>
+    <t>버스 드라이버 자체 특성, FSM이 기다리는 값 아님</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>SDA/SCL fall time (물리적 특성)</t>
+  </si>
+  <si>
+    <t>TAA</t>
+  </si>
+  <si>
+    <t>Read 시 SCL 이후 데이터 유효 시점(MAX)</t>
+  </si>
+  <si>
+    <t>TLOW(1300ns)가 더 크므로 자동으로 만족됨</t>
+  </si>
+  <si>
+    <t>검증만, 별도 대기 불필요</t>
+  </si>
+  <si>
+    <t>TWC</t>
+  </si>
+  <si>
+    <t>Write cycle time (MAX)</t>
+  </si>
+  <si>
+    <t>5ms</t>
+  </si>
+  <si>
+    <t>ACK Polling으로 처리 (분주기 카운터 아님)</t>
+  </si>
+  <si>
     <t>THIGH</t>
-  </si>
-  <si>
-    <t>SCL High 최소 유지시간</t>
-  </si>
-  <si>
-    <t>ClkDivider: SCL High 상태 유지 클럭 수</t>
-  </si>
-  <si>
-    <t>TLOW</t>
-  </si>
-  <si>
-    <t>SCL Low 최소 유지시간</t>
-  </si>
-  <si>
-    <t>ClkDivider: SCL Low 상태 유지 클럭 수</t>
-  </si>
-  <si>
-    <t>THD:STA</t>
-  </si>
-  <si>
-    <t>START 생성 후 첫 SCL Low까지 대기</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: START 직후 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>TSU:STA</t>
-  </si>
-  <si>
-    <t>(Repeated)START 전 SDA High 유지</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: Repeated START 전 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>TSU:DAT</t>
-  </si>
-  <si>
-    <t>SDA 변경 후 SCL 상승까지 여유</t>
-  </si>
-  <si>
-    <t>BitTxRx: SDA 바꾼 후 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>보통 TLOW 안에서 자동 확보됨</t>
-  </si>
-  <si>
-    <t>THD:DAT</t>
-  </si>
-  <si>
-    <t>SCL 하강 후 SDA 변경까지 여유</t>
-  </si>
-  <si>
-    <t>BitTxRx: 사실상 제약 없음</t>
-  </si>
-  <si>
-    <t>0이라 대기 불필요</t>
-  </si>
-  <si>
-    <t>TSU:STO</t>
-  </si>
-  <si>
-    <t>STOP 생성 전 SCL High 유지</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: STOP 만들기 전 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>TBUF</t>
-  </si>
-  <si>
-    <t>STOP~다음 START 최소 간격</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: 트랜잭션 사이 최소 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>참고용 (FSM 카운터에 직접 안 들어감)</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>SDA/SCL rise time (물리적 특성)</t>
-  </si>
-  <si>
-    <t>버스 드라이버 자체 특성, FSM이 기다리는 값 아님</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>TF</t>
-  </si>
-  <si>
-    <t>SDA/SCL fall time (물리적 특성)</t>
-  </si>
-  <si>
-    <t>TAA</t>
-  </si>
-  <si>
-    <t>Read 시 SCL 이후 데이터 유효 시점(MAX)</t>
-  </si>
-  <si>
-    <t>TLOW(1300ns)가 더 크므로 자동으로 만족됨</t>
-  </si>
-  <si>
-    <t>검증만, 별도 대기 불필요</t>
-  </si>
-  <si>
-    <t>TWC</t>
-  </si>
-  <si>
-    <t>Write cycle time (MAX)</t>
-  </si>
-  <si>
-    <t>5ms</t>
-  </si>
-  <si>
-    <t>ACK Polling으로 처리 (분주기 카운터 아님)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -249,6 +250,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>58066</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2199409</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>32052</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4560793"/>
+          <a:ext cx="15880773" cy="6502941"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,7 +618,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="65.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.77734375" customWidth="1"/>
@@ -585,7 +629,7 @@
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -631,7 +675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -654,7 +698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -677,295 +721,295 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
       </c>
       <c r="C7">
         <v>600</v>
       </c>
       <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
       </c>
       <c r="C8">
         <v>1300</v>
       </c>
       <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
       <c r="C9">
         <v>600</v>
       </c>
       <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="E9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
       </c>
       <c r="C10">
         <v>600</v>
       </c>
       <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
       </c>
       <c r="C13">
         <v>600</v>
       </c>
       <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
       </c>
       <c r="C14">
         <v>1300</v>
       </c>
       <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
       </c>
       <c r="C17">
         <v>300</v>
       </c>
       <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>48</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
       </c>
       <c r="C19">
         <v>900</v>
       </c>
       <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
         <v>51</v>
       </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>53</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>55</v>
       </c>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
       <c r="E20" t="s">
         <v>1</v>
       </c>
@@ -973,14 +1017,15 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G20" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G6 A8:G20 B7:G7" numberStoredAsText="1"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/참고사항/SysClk_Timing_Calc.xlsx
+++ b/참고사항/SysClk_Timing_Calc.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLUE\work\VHDL\FSM_EEPROM\참고사항\"/>
@@ -63,133 +63,134 @@
     <t>필요 최소 클럭 수 (값÷20, 올림)</t>
   </si>
   <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>SCL High 최소 유지시간</t>
+  </si>
+  <si>
+    <t>ClkDivider: SCL High 상태 유지 클럭 수</t>
+  </si>
+  <si>
+    <t>TLOW</t>
+  </si>
+  <si>
+    <t>SCL Low 최소 유지시간</t>
+  </si>
+  <si>
+    <t>ClkDivider: SCL Low 상태 유지 클럭 수</t>
+  </si>
+  <si>
+    <t>THD:STA</t>
+  </si>
+  <si>
+    <t>START 생성 후 첫 SCL Low까지 대기</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: START 직후 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>TSU:STA</t>
+  </si>
+  <si>
+    <t>(Repeated)START 전 SDA High 유지</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: Repeated START 전 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>TSU:DAT</t>
+  </si>
+  <si>
+    <t>SDA 변경 후 SCL 상승까지 여유</t>
+  </si>
+  <si>
+    <t>BitTxRx: SDA 바꾼 후 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>보통 TLOW 안에서 자동 확보됨</t>
+  </si>
+  <si>
+    <t>THD:DAT</t>
+  </si>
+  <si>
+    <t>SCL 하강 후 SDA 변경까지 여유</t>
+  </si>
+  <si>
+    <t>BitTxRx: 사실상 제약 없음</t>
+  </si>
+  <si>
+    <t>0이라 대기 불필요</t>
+  </si>
+  <si>
+    <t>TSU:STO</t>
+  </si>
+  <si>
+    <t>STOP 생성 전 SCL High 유지</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: STOP 만들기 전 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>TBUF</t>
+  </si>
+  <si>
+    <t>STOP~다음 START 최소 간격</t>
+  </si>
+  <si>
+    <t>커맨드 FSM: 트랜잭션 사이 최소 대기 클럭 수</t>
+  </si>
+  <si>
+    <t>참고용 (FSM 카운터에 직접 안 들어감)</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>SDA/SCL rise time (물리적 특성)</t>
+  </si>
+  <si>
+    <t>버스 드라이버 자체 특성, FSM이 기다리는 값 아님</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>SDA/SCL fall time (물리적 특성)</t>
+  </si>
+  <si>
+    <t>TAA</t>
+  </si>
+  <si>
+    <t>Read 시 SCL 이후 데이터 유효 시점(MAX)</t>
+  </si>
+  <si>
+    <t>TLOW(1300ns)가 더 크므로 자동으로 만족됨</t>
+  </si>
+  <si>
+    <t>검증만, 별도 대기 불필요</t>
+  </si>
+  <si>
+    <t>TWC</t>
+  </si>
+  <si>
+    <t>Write cycle time (MAX)</t>
+  </si>
+  <si>
+    <t>5ms</t>
+  </si>
+  <si>
+    <t>ACK Polling으로 처리 (분주기 카운터 아님)</t>
+  </si>
+  <si>
+    <t>THIGH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>실제 채택 클럭 수(여유 포함)</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>SCL High 최소 유지시간</t>
-  </si>
-  <si>
-    <t>ClkDivider: SCL High 상태 유지 클럭 수</t>
-  </si>
-  <si>
-    <t>TLOW</t>
-  </si>
-  <si>
-    <t>SCL Low 최소 유지시간</t>
-  </si>
-  <si>
-    <t>ClkDivider: SCL Low 상태 유지 클럭 수</t>
-  </si>
-  <si>
-    <t>THD:STA</t>
-  </si>
-  <si>
-    <t>START 생성 후 첫 SCL Low까지 대기</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: START 직후 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>TSU:STA</t>
-  </si>
-  <si>
-    <t>(Repeated)START 전 SDA High 유지</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: Repeated START 전 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>TSU:DAT</t>
-  </si>
-  <si>
-    <t>SDA 변경 후 SCL 상승까지 여유</t>
-  </si>
-  <si>
-    <t>BitTxRx: SDA 바꾼 후 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>보통 TLOW 안에서 자동 확보됨</t>
-  </si>
-  <si>
-    <t>THD:DAT</t>
-  </si>
-  <si>
-    <t>SCL 하강 후 SDA 변경까지 여유</t>
-  </si>
-  <si>
-    <t>BitTxRx: 사실상 제약 없음</t>
-  </si>
-  <si>
-    <t>0이라 대기 불필요</t>
-  </si>
-  <si>
-    <t>TSU:STO</t>
-  </si>
-  <si>
-    <t>STOP 생성 전 SCL High 유지</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: STOP 만들기 전 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>TBUF</t>
-  </si>
-  <si>
-    <t>STOP~다음 START 최소 간격</t>
-  </si>
-  <si>
-    <t>커맨드 FSM: 트랜잭션 사이 최소 대기 클럭 수</t>
-  </si>
-  <si>
-    <t>참고용 (FSM 카운터에 직접 안 들어감)</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>SDA/SCL rise time (물리적 특성)</t>
-  </si>
-  <si>
-    <t>버스 드라이버 자체 특성, FSM이 기다리는 값 아님</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>TF</t>
-  </si>
-  <si>
-    <t>SDA/SCL fall time (물리적 특성)</t>
-  </si>
-  <si>
-    <t>TAA</t>
-  </si>
-  <si>
-    <t>Read 시 SCL 이후 데이터 유효 시점(MAX)</t>
-  </si>
-  <si>
-    <t>TLOW(1300ns)가 더 크므로 자동으로 만족됨</t>
-  </si>
-  <si>
-    <t>검증만, 별도 대기 불필요</t>
-  </si>
-  <si>
-    <t>TWC</t>
-  </si>
-  <si>
-    <t>Write cycle time (MAX)</t>
-  </si>
-  <si>
-    <t>5ms</t>
-  </si>
-  <si>
-    <t>ACK Polling으로 처리 (분주기 카운터 아님)</t>
-  </si>
-  <si>
-    <t>THIGH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -263,7 +264,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2199409</xdr:colOff>
+      <xdr:colOff>1213291</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>32052</xdr:rowOff>
     </xdr:to>
@@ -617,16 +618,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="65.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="1" max="1" width="65.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.77734375" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -715,24 +717,24 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>600</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>1</v>
@@ -746,16 +748,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
       </c>
       <c r="C8">
         <v>1300</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>1</v>
@@ -769,16 +771,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
       </c>
       <c r="C9">
         <v>600</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -792,16 +794,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
       </c>
       <c r="C10">
         <v>600</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
         <v>1</v>
@@ -815,62 +817,62 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
         <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
       </c>
       <c r="C13">
         <v>600</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -884,16 +886,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
       </c>
       <c r="C14">
         <v>1300</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -907,7 +909,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
@@ -930,86 +932,86 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
       </c>
       <c r="C17">
         <v>300</v>
       </c>
       <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
         <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
       <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
         <v>44</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
       </c>
       <c r="C19">
         <v>900</v>
       </c>
       <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
         <v>50</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
         <v>52</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>53</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>54</v>
       </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
       <c r="E20" t="s">
         <v>1</v>
       </c>
@@ -1017,14 +1019,14 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G6 A8:G20 B7:G7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G5 A8:G20 B7:G7 A6:E6 G6" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/참고사항/SysClk_Timing_Calc.xlsx
+++ b/참고사항/SysClk_Timing_Calc.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
   <si>
     <t>SysClk 타이밍 계산표</t>
   </si>
@@ -736,8 +736,9 @@
       <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>1</v>
+      <c r="E7">
+        <f>C7/20</f>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>1</v>
@@ -759,8 +760,9 @@
       <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" t="s">
-        <v>1</v>
+      <c r="E8">
+        <f t="shared" ref="E8:E20" si="0">C8/20</f>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
         <v>1</v>
@@ -782,8 +784,9 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>1</v>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>1</v>
@@ -805,8 +808,9 @@
       <c r="D10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
-        <v>1</v>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
         <v>1</v>
@@ -828,8 +832,9 @@
       <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
-        <v>1</v>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>1</v>
@@ -851,8 +856,9 @@
       <c r="D12" t="s">
         <v>32</v>
       </c>
-      <c r="E12" t="s">
-        <v>1</v>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F12" t="s">
         <v>1</v>
@@ -874,8 +880,9 @@
       <c r="D13" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
-        <v>1</v>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>1</v>
@@ -897,14 +904,21 @@
       <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="E14" t="s">
-        <v>1</v>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="F14" t="s">
         <v>1</v>
       </c>
       <c r="G14" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -920,8 +934,9 @@
       <c r="D16" t="s">
         <v>1</v>
       </c>
-      <c r="E16" t="s">
-        <v>1</v>
+      <c r="E16" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="F16" t="s">
         <v>1</v>
@@ -943,8 +958,9 @@
       <c r="D17" t="s">
         <v>43</v>
       </c>
-      <c r="E17" t="s">
-        <v>1</v>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>1</v>
@@ -966,8 +982,9 @@
       <c r="D18" t="s">
         <v>43</v>
       </c>
-      <c r="E18" t="s">
-        <v>1</v>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
         <v>1</v>
@@ -989,8 +1006,9 @@
       <c r="D19" t="s">
         <v>49</v>
       </c>
-      <c r="E19" t="s">
-        <v>1</v>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
         <v>1</v>
@@ -1012,8 +1030,9 @@
       <c r="D20" t="s">
         <v>54</v>
       </c>
-      <c r="E20" t="s">
-        <v>1</v>
+      <c r="E20" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="F20" t="s">
         <v>1</v>
@@ -1025,9 +1044,10 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G5 A8:G20 B7:G7 A6:E6 G6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G5 A15:D20 B7:D7 A6:E6 G6 F7:G7 A8:D14 F8:G14 F15:G20" numberStoredAsText="1"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>